--- a/docs/perechen-otchetov/obrazcy/ФО-05.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-05.xlsx
@@ -677,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -876,25 +876,25 @@
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>9805.365</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>2812.98219</v>
+        <v>2850.00939</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>2310.90477</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>493.67742</v>
+        <v>530.70462</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>8.4</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>12618.34719</v>
+        <v>12655.37439</v>
       </c>
       <c r="N8" s="10" t="n"/>
       <c r="O8" s="6" t="n"/>
@@ -919,25 +919,25 @@
       </c>
       <c r="B9" s="12" t="n"/>
       <c r="C9" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>4182.99</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1769.96283</v>
+        <v>1806.99003</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>1518.16667</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>243.39616</v>
+        <v>280.42336</v>
       </c>
       <c r="J9" s="14" t="n">
         <v>8.4</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>5952.95283</v>
+        <v>5989.98003</v>
       </c>
       <c r="N9" s="15" t="n"/>
       <c r="O9" s="11" t="n"/>
@@ -962,25 +962,25 @@
       </c>
       <c r="B10" s="17" t="n"/>
       <c r="C10" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>4182.99</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>1769.96283</v>
+        <v>1806.99003</v>
       </c>
       <c r="H10" s="19" t="n">
         <v>1518.16667</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>243.39616</v>
+        <v>280.42336</v>
       </c>
       <c r="J10" s="19" t="n">
         <v>8.4</v>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>5952.95283</v>
+        <v>5989.98003</v>
       </c>
       <c r="N10" s="20" t="n"/>
       <c r="O10" s="21" t="n"/>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="B44" s="23" t="n"/>
       <c r="C44" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="25" t="n">
-        <v>459.557</v>
+        <v>496.5842</v>
       </c>
       <c r="H44" s="25" t="n">
         <v>437.5</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>22.057</v>
+        <v>59.0842</v>
       </c>
       <c r="J44" s="25" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="25" t="n">
-        <v>459.557</v>
+        <v>496.5842</v>
       </c>
       <c r="N44" s="26" t="n"/>
       <c r="O44" s="27" t="n"/>
@@ -2386,7 +2386,7 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="28" t="inlineStr">
         <is>
-          <t>ОсОО «Кут-Мүлк»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B45" s="29" t="n"/>
@@ -2401,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="32" t="n">
-        <v>459.557</v>
+        <v>37.0272</v>
       </c>
       <c r="H45" s="32" t="n">
-        <v>437.5</v>
+        <v>0</v>
       </c>
       <c r="I45" s="32" t="n">
-        <v>22.057</v>
+        <v>37.0272</v>
       </c>
       <c r="J45" s="32" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="32" t="n">
-        <v>459.557</v>
+        <v>37.0272</v>
       </c>
       <c r="N45" s="30" t="n"/>
       <c r="O45" s="33" t="n"/>
@@ -2427,7 +2427,7 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>№ 23-1/019 от 05.05.2023, USD</t>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
         </is>
       </c>
       <c r="B46" s="29" t="n"/>
@@ -2440,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="32" t="n">
-        <v>459.557</v>
+        <v>37.0272</v>
       </c>
       <c r="H46" s="32" t="n">
-        <v>437.5</v>
+        <v>0</v>
       </c>
       <c r="I46" s="32" t="n">
-        <v>22.057</v>
+        <v>37.0272</v>
       </c>
       <c r="J46" s="32" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="32" t="n">
-        <v>459.557</v>
+        <v>37.0272</v>
       </c>
       <c r="N46" s="30" t="n"/>
       <c r="O46" s="33" t="n"/>
@@ -2466,7 +2466,7 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="41" t="inlineStr">
         <is>
-          <t>в тыс. USD (курс 87,50000)</t>
+          <t>в тыс. EUR (курс 101,50000)</t>
         </is>
       </c>
       <c r="B47" s="42" t="n"/>
@@ -2477,13 +2477,13 @@
         <v>0</v>
       </c>
       <c r="G47" s="44" t="n">
-        <v>5.25208</v>
+        <v>0.3648</v>
       </c>
       <c r="H47" s="44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I47" s="44" t="n">
-        <v>0.25208</v>
+        <v>0.3648</v>
       </c>
       <c r="J47" s="44" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="44" t="n">
-        <v>5.25208</v>
+        <v>0.3648</v>
       </c>
       <c r="N47" s="43" t="n"/>
       <c r="O47" s="45" t="n"/>
@@ -2503,11 +2503,11 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="35" t="inlineStr">
         <is>
-          <t>платёж 05.10.2026</t>
+          <t>платёж 20.10.2026</t>
         </is>
       </c>
       <c r="B48" s="36" t="n">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="C48" s="37" t="n"/>
       <c r="D48" s="37" t="n"/>
@@ -2516,13 +2516,13 @@
       </c>
       <c r="F48" s="37" t="n"/>
       <c r="G48" s="39" t="n">
-        <v>459.557</v>
+        <v>37.0272</v>
       </c>
       <c r="H48" s="39" t="n">
-        <v>437.5</v>
+        <v>0</v>
       </c>
       <c r="I48" s="39" t="n">
-        <v>22.057</v>
+        <v>37.0272</v>
       </c>
       <c r="J48" s="39" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="39" t="n">
-        <v>459.557</v>
+        <v>37.0272</v>
       </c>
       <c r="N48" s="37" t="n"/>
       <c r="O48" s="40" t="inlineStr">
@@ -2544,307 +2544,305 @@
       </c>
     </row>
     <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Кут-Мүлк»</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="32" t="n">
+        <v>459.557</v>
+      </c>
+      <c r="H49" s="32" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="I49" s="32" t="n">
+        <v>22.057</v>
+      </c>
+      <c r="J49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="32" t="n">
+        <v>459.557</v>
+      </c>
+      <c r="N49" s="30" t="n"/>
+      <c r="O49" s="33" t="n"/>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>№ 23-1/019 от 05.05.2023, USD</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="30" t="n"/>
+      <c r="D50" s="30" t="n"/>
+      <c r="E50" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="32" t="n">
+        <v>459.557</v>
+      </c>
+      <c r="H50" s="32" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="I50" s="32" t="n">
+        <v>22.057</v>
+      </c>
+      <c r="J50" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="32" t="n">
+        <v>459.557</v>
+      </c>
+      <c r="N50" s="30" t="n"/>
+      <c r="O50" s="33" t="n"/>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="n"/>
+      <c r="C51" s="43" t="n"/>
+      <c r="D51" s="43" t="n"/>
+      <c r="E51" s="43" t="n"/>
+      <c r="F51" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="44" t="n">
+        <v>5.25208</v>
+      </c>
+      <c r="H51" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="I51" s="44" t="n">
+        <v>0.25208</v>
+      </c>
+      <c r="J51" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="44" t="n">
+        <v>5.25208</v>
+      </c>
+      <c r="N51" s="43" t="n"/>
+      <c r="O51" s="45" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>платёж 05.10.2026</t>
+        </is>
+      </c>
+      <c r="B52" s="36" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C52" s="37" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="37" t="n"/>
+      <c r="G52" s="39" t="n">
+        <v>459.557</v>
+      </c>
+      <c r="H52" s="39" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="I52" s="39" t="n">
+        <v>22.057</v>
+      </c>
+      <c r="J52" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="39" t="n">
+        <v>459.557</v>
+      </c>
+      <c r="N52" s="37" t="n"/>
+      <c r="O52" s="40" t="inlineStr">
+        <is>
+          <t>Не наступил</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Департамент регионального развития</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="13" t="n">
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D53" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E53" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="F49" s="14" t="n">
+      <c r="F53" s="14" t="n">
         <v>5622.375</v>
       </c>
-      <c r="G49" s="14" t="n">
+      <c r="G53" s="14" t="n">
         <v>1043.01936</v>
       </c>
-      <c r="H49" s="14" t="n">
+      <c r="H53" s="14" t="n">
         <v>792.7381</v>
       </c>
-      <c r="I49" s="14" t="n">
+      <c r="I53" s="14" t="n">
         <v>250.28126</v>
       </c>
-      <c r="J49" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="14" t="n">
+      <c r="J53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="14" t="n">
         <v>6665.39436</v>
       </c>
-      <c r="N49" s="15" t="n"/>
-      <c r="O49" s="11" t="n"/>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="N53" s="15" t="n"/>
+      <c r="O53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Отдел развития регионов</t>
         </is>
       </c>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="18" t="n">
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="D54" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E54" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="F50" s="19" t="n">
+      <c r="F54" s="19" t="n">
         <v>3796.875</v>
       </c>
-      <c r="G50" s="19" t="n">
+      <c r="G54" s="19" t="n">
         <v>795.3526900000001</v>
       </c>
-      <c r="H50" s="19" t="n">
+      <c r="H54" s="19" t="n">
         <v>616.07143</v>
       </c>
-      <c r="I50" s="19" t="n">
+      <c r="I54" s="19" t="n">
         <v>179.28126</v>
       </c>
-      <c r="J50" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="19" t="n">
+      <c r="J54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="19" t="n">
         <v>4592.22769</v>
       </c>
-      <c r="N50" s="20" t="n"/>
-      <c r="O50" s="21" t="n"/>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="N54" s="20" t="n"/>
+      <c r="O54" s="21" t="n"/>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>Осмонов Б. Т.</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="24" t="n">
+      <c r="B55" s="23" t="n"/>
+      <c r="C55" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="D51" s="24" t="n">
+      <c r="D55" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E55" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="F51" s="25" t="n">
+      <c r="F55" s="25" t="n">
         <v>3276.875</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G55" s="25" t="n">
         <v>540.6994099999999</v>
       </c>
-      <c r="H51" s="25" t="n">
+      <c r="H55" s="25" t="n">
         <v>408.92857</v>
       </c>
-      <c r="I51" s="25" t="n">
+      <c r="I55" s="25" t="n">
         <v>131.77084</v>
       </c>
-      <c r="J51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="25" t="n">
+      <c r="J55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="25" t="n">
         <v>3817.57441</v>
       </c>
-      <c r="N51" s="26" t="n"/>
-      <c r="O51" s="27" t="n"/>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
+      <c r="N55" s="26" t="n"/>
+      <c r="O55" s="27" t="n"/>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>ОсОО «Ак-Булак»</t>
-        </is>
-      </c>
-      <c r="B52" s="29" t="n"/>
-      <c r="C52" s="30" t="n"/>
-      <c r="D52" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="32" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="H52" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I52" s="32" t="n">
-        <v>24.16667</v>
-      </c>
-      <c r="J52" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="32" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="N52" s="30" t="n"/>
-      <c r="O52" s="33" t="n"/>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>№ 24-6/019 от 11.02.2024, KGS</t>
-        </is>
-      </c>
-      <c r="B53" s="29" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="30" t="n"/>
-      <c r="E53" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="32" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="H53" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" s="32" t="n">
-        <v>24.16667</v>
-      </c>
-      <c r="J53" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="32" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="N53" s="30" t="n"/>
-      <c r="O53" s="33" t="n"/>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="35" t="inlineStr">
-        <is>
-          <t>платёж 11.10.2026</t>
-        </is>
-      </c>
-      <c r="B54" s="36" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C54" s="37" t="n"/>
-      <c r="D54" s="37" t="n"/>
-      <c r="E54" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="37" t="n"/>
-      <c r="G54" s="39" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="H54" s="39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I54" s="39" t="n">
-        <v>24.16667</v>
-      </c>
-      <c r="J54" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="39" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="N54" s="37" t="n"/>
-      <c r="O54" s="40" t="inlineStr">
-        <is>
-          <t>Не наступил</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Алтын-Тоо»</t>
-        </is>
-      </c>
-      <c r="B55" s="29" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="32" t="n">
-        <v>16.66667</v>
-      </c>
-      <c r="H55" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="32" t="n">
-        <v>16.66667</v>
-      </c>
-      <c r="J55" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="32" t="n">
-        <v>16.66667</v>
-      </c>
-      <c r="N55" s="30" t="n"/>
-      <c r="O55" s="33" t="n"/>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="34" t="inlineStr">
-        <is>
-          <t>№ 24-2/088 от 12.03.2024, KGS</t>
         </is>
       </c>
       <c r="B56" s="29" t="n"/>
       <c r="C56" s="30" t="n"/>
-      <c r="D56" s="30" t="n"/>
+      <c r="D56" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="E56" s="31" t="n">
         <v>1</v>
       </c>
@@ -2852,13 +2850,13 @@
         <v>0</v>
       </c>
       <c r="G56" s="32" t="n">
-        <v>16.66667</v>
+        <v>74.16667</v>
       </c>
       <c r="H56" s="32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I56" s="32" t="n">
-        <v>16.66667</v>
+        <v>24.16667</v>
       </c>
       <c r="J56" s="32" t="n">
         <v>0</v>
@@ -2870,104 +2868,104 @@
         <v>0</v>
       </c>
       <c r="M56" s="32" t="n">
-        <v>16.66667</v>
+        <v>74.16667</v>
       </c>
       <c r="N56" s="30" t="n"/>
       <c r="O56" s="33" t="n"/>
     </row>
     <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="35" t="inlineStr">
-        <is>
-          <t>платёж 12.10.2026</t>
-        </is>
-      </c>
-      <c r="B57" s="36" t="n">
-        <v>46307</v>
-      </c>
-      <c r="C57" s="37" t="n"/>
-      <c r="D57" s="37" t="n"/>
-      <c r="E57" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="37" t="n"/>
-      <c r="G57" s="39" t="n">
-        <v>16.66667</v>
-      </c>
-      <c r="H57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="39" t="n">
-        <v>16.66667</v>
-      </c>
-      <c r="J57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="39" t="n">
-        <v>16.66667</v>
-      </c>
-      <c r="N57" s="37" t="n"/>
-      <c r="O57" s="40" t="inlineStr">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>№ 24-6/019 от 11.02.2024, KGS</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="30" t="n"/>
+      <c r="E57" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="32" t="n">
+        <v>74.16667</v>
+      </c>
+      <c r="H57" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" s="32" t="n">
+        <v>24.16667</v>
+      </c>
+      <c r="J57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="32" t="n">
+        <v>74.16667</v>
+      </c>
+      <c r="N57" s="30" t="n"/>
+      <c r="O57" s="33" t="n"/>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="35" t="inlineStr">
+        <is>
+          <t>платёж 11.10.2026</t>
+        </is>
+      </c>
+      <c r="B58" s="36" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C58" s="37" t="n"/>
+      <c r="D58" s="37" t="n"/>
+      <c r="E58" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="37" t="n"/>
+      <c r="G58" s="39" t="n">
+        <v>74.16667</v>
+      </c>
+      <c r="H58" s="39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" s="39" t="n">
+        <v>24.16667</v>
+      </c>
+      <c r="J58" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="39" t="n">
+        <v>74.16667</v>
+      </c>
+      <c r="N58" s="37" t="n"/>
+      <c r="O58" s="40" t="inlineStr">
         <is>
           <t>Не наступил</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Достук Строй»</t>
-        </is>
-      </c>
-      <c r="B58" s="29" t="n"/>
-      <c r="C58" s="30" t="n"/>
-      <c r="D58" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="32" t="n">
-        <v>49.16667</v>
-      </c>
-      <c r="H58" s="32" t="n">
-        <v>41.66667</v>
-      </c>
-      <c r="I58" s="32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J58" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="32" t="n">
-        <v>49.16667</v>
-      </c>
-      <c r="N58" s="30" t="n"/>
-      <c r="O58" s="33" t="n"/>
-    </row>
     <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
-        <is>
-          <t>№ 26-5/090 от 08.09.2026, KGS</t>
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Алтын-Тоо»</t>
         </is>
       </c>
       <c r="B59" s="29" t="n"/>
       <c r="C59" s="30" t="n"/>
-      <c r="D59" s="30" t="n"/>
+      <c r="D59" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="E59" s="31" t="n">
         <v>1</v>
       </c>
@@ -2975,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="G59" s="32" t="n">
-        <v>49.16667</v>
+        <v>16.66667</v>
       </c>
       <c r="H59" s="32" t="n">
-        <v>41.66667</v>
+        <v>0</v>
       </c>
       <c r="I59" s="32" t="n">
-        <v>7.5</v>
+        <v>16.66667</v>
       </c>
       <c r="J59" s="32" t="n">
         <v>0</v>
@@ -2993,120 +2991,118 @@
         <v>0</v>
       </c>
       <c r="M59" s="32" t="n">
-        <v>49.16667</v>
+        <v>16.66667</v>
       </c>
       <c r="N59" s="30" t="n"/>
       <c r="O59" s="33" t="n"/>
     </row>
     <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>платёж 15.10.2026</t>
-        </is>
-      </c>
-      <c r="B60" s="36" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C60" s="37" t="n"/>
-      <c r="D60" s="37" t="n"/>
-      <c r="E60" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="37" t="n"/>
-      <c r="G60" s="39" t="n">
-        <v>49.16667</v>
-      </c>
-      <c r="H60" s="39" t="n">
-        <v>41.66667</v>
-      </c>
-      <c r="I60" s="39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J60" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="39" t="n">
-        <v>49.16667</v>
-      </c>
-      <c r="N60" s="37" t="n"/>
-      <c r="O60" s="40" t="inlineStr">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>№ 24-2/088 от 12.03.2024, KGS</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="30" t="n"/>
+      <c r="D60" s="30" t="n"/>
+      <c r="E60" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="32" t="n">
+        <v>16.66667</v>
+      </c>
+      <c r="H60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="32" t="n">
+        <v>16.66667</v>
+      </c>
+      <c r="J60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="32" t="n">
+        <v>16.66667</v>
+      </c>
+      <c r="N60" s="30" t="n"/>
+      <c r="O60" s="33" t="n"/>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="35" t="inlineStr">
+        <is>
+          <t>платёж 12.10.2026</t>
+        </is>
+      </c>
+      <c r="B61" s="36" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C61" s="37" t="n"/>
+      <c r="D61" s="37" t="n"/>
+      <c r="E61" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="37" t="n"/>
+      <c r="G61" s="39" t="n">
+        <v>16.66667</v>
+      </c>
+      <c r="H61" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="39" t="n">
+        <v>16.66667</v>
+      </c>
+      <c r="J61" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="39" t="n">
+        <v>16.66667</v>
+      </c>
+      <c r="N61" s="37" t="n"/>
+      <c r="O61" s="40" t="inlineStr">
         <is>
           <t>Не наступил</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Кербен-Жибек»</t>
-        </is>
-      </c>
-      <c r="B61" s="29" t="n"/>
-      <c r="C61" s="30" t="n"/>
-      <c r="D61" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F61" s="32" t="n">
-        <v>1666.875</v>
-      </c>
-      <c r="G61" s="32" t="n">
-        <v>191.77083</v>
-      </c>
-      <c r="H61" s="32" t="n">
-        <v>145.83333</v>
-      </c>
-      <c r="I61" s="32" t="n">
-        <v>45.9375</v>
-      </c>
-      <c r="J61" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="32" t="n">
-        <v>1858.64583</v>
-      </c>
-      <c r="N61" s="31" t="n">
-        <v>245</v>
-      </c>
-      <c r="O61" s="33" t="n"/>
-    </row>
     <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="34" t="inlineStr">
-        <is>
-          <t>№ 20-5/118 от 23.06.2020, USD</t>
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Достук Строй»</t>
         </is>
       </c>
       <c r="B62" s="29" t="n"/>
       <c r="C62" s="30" t="n"/>
-      <c r="D62" s="30" t="n"/>
+      <c r="D62" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="E62" s="31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F62" s="32" t="n">
-        <v>1666.875</v>
+        <v>0</v>
       </c>
       <c r="G62" s="32" t="n">
-        <v>191.77083</v>
+        <v>49.16667</v>
       </c>
       <c r="H62" s="32" t="n">
-        <v>145.83333</v>
+        <v>41.66667</v>
       </c>
       <c r="I62" s="32" t="n">
-        <v>45.9375</v>
+        <v>7.5</v>
       </c>
       <c r="J62" s="32" t="n">
         <v>0</v>
@@ -3118,250 +3114,250 @@
         <v>0</v>
       </c>
       <c r="M62" s="32" t="n">
-        <v>1858.64583</v>
-      </c>
-      <c r="N62" s="31" t="n">
-        <v>245</v>
-      </c>
+        <v>49.16667</v>
+      </c>
+      <c r="N62" s="30" t="n"/>
       <c r="O62" s="33" t="n"/>
     </row>
     <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="41" t="inlineStr">
-        <is>
-          <t>в тыс. USD (курс 87,50000)</t>
-        </is>
-      </c>
-      <c r="B63" s="42" t="n"/>
-      <c r="C63" s="43" t="n"/>
-      <c r="D63" s="43" t="n"/>
-      <c r="E63" s="43" t="n"/>
-      <c r="F63" s="44" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="G63" s="44" t="n">
-        <v>2.19167</v>
-      </c>
-      <c r="H63" s="44" t="n">
-        <v>1.66667</v>
-      </c>
-      <c r="I63" s="44" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="J63" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="44" t="n">
-        <v>21.24167</v>
-      </c>
-      <c r="N63" s="43" t="n"/>
-      <c r="O63" s="45" t="n"/>
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>№ 26-5/090 от 08.09.2026, KGS</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="30" t="n"/>
+      <c r="D63" s="30" t="n"/>
+      <c r="E63" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>49.16667</v>
+      </c>
+      <c r="H63" s="32" t="n">
+        <v>41.66667</v>
+      </c>
+      <c r="I63" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>49.16667</v>
+      </c>
+      <c r="N63" s="30" t="n"/>
+      <c r="O63" s="33" t="n"/>
     </row>
     <row r="64" ht="13" customHeight="1">
       <c r="A64" s="35" t="inlineStr">
         <is>
-          <t>не оплачено до 01.10.2026, в суде</t>
+          <t>платёж 15.10.2026</t>
         </is>
       </c>
       <c r="B64" s="36" t="n">
-        <v>46051</v>
+        <v>46310</v>
       </c>
       <c r="C64" s="37" t="n"/>
       <c r="D64" s="37" t="n"/>
       <c r="E64" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="37" t="n"/>
+      <c r="G64" s="39" t="n">
+        <v>49.16667</v>
+      </c>
+      <c r="H64" s="39" t="n">
+        <v>41.66667</v>
+      </c>
+      <c r="I64" s="39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J64" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="39" t="n">
+        <v>49.16667</v>
+      </c>
+      <c r="N64" s="37" t="n"/>
+      <c r="O64" s="40" t="inlineStr">
+        <is>
+          <t>Не наступил</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Кербен-Жибек»</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="n"/>
+      <c r="C65" s="30" t="n"/>
+      <c r="D65" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>1666.875</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>191.77083</v>
+      </c>
+      <c r="H65" s="32" t="n">
+        <v>145.83333</v>
+      </c>
+      <c r="I65" s="32" t="n">
+        <v>45.9375</v>
+      </c>
+      <c r="J65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>1858.64583</v>
+      </c>
+      <c r="N65" s="31" t="n">
+        <v>245</v>
+      </c>
+      <c r="O65" s="33" t="n"/>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>№ 20-5/118 от 23.06.2020, USD</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="n"/>
+      <c r="C66" s="30" t="n"/>
+      <c r="D66" s="30" t="n"/>
+      <c r="E66" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>1666.875</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>191.77083</v>
+      </c>
+      <c r="H66" s="32" t="n">
+        <v>145.83333</v>
+      </c>
+      <c r="I66" s="32" t="n">
+        <v>45.9375</v>
+      </c>
+      <c r="J66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>1858.64583</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>245</v>
+      </c>
+      <c r="O66" s="33" t="n"/>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="41" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B67" s="42" t="n"/>
+      <c r="C67" s="43" t="n"/>
+      <c r="D67" s="43" t="n"/>
+      <c r="E67" s="43" t="n"/>
+      <c r="F67" s="44" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="G67" s="44" t="n">
+        <v>2.19167</v>
+      </c>
+      <c r="H67" s="44" t="n">
+        <v>1.66667</v>
+      </c>
+      <c r="I67" s="44" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="J67" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="44" t="n">
+        <v>21.24167</v>
+      </c>
+      <c r="N67" s="43" t="n"/>
+      <c r="O67" s="45" t="n"/>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="35" t="inlineStr">
+        <is>
+          <t>не оплачено до 01.10.2026, в суде</t>
+        </is>
+      </c>
+      <c r="B68" s="36" t="n">
+        <v>46051</v>
+      </c>
+      <c r="C68" s="37" t="n"/>
+      <c r="D68" s="37" t="n"/>
+      <c r="E68" s="38" t="n">
         <v>8</v>
       </c>
-      <c r="F64" s="39" t="n">
+      <c r="F68" s="39" t="n">
         <v>1481.66667</v>
       </c>
-      <c r="G64" s="37" t="n"/>
-      <c r="H64" s="37" t="n"/>
-      <c r="I64" s="37" t="n"/>
-      <c r="J64" s="37" t="n"/>
-      <c r="K64" s="37" t="n"/>
-      <c r="L64" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="39" t="n">
+      <c r="G68" s="37" t="n"/>
+      <c r="H68" s="37" t="n"/>
+      <c r="I68" s="37" t="n"/>
+      <c r="J68" s="37" t="n"/>
+      <c r="K68" s="37" t="n"/>
+      <c r="L68" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="39" t="n">
         <v>1481.66667</v>
       </c>
-      <c r="N64" s="38" t="n">
+      <c r="N68" s="38" t="n">
         <v>245</v>
       </c>
-      <c r="O64" s="40" t="inlineStr">
+      <c r="O68" s="40" t="inlineStr">
         <is>
           <t>Предъявлен в суд</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="35" t="inlineStr">
-        <is>
-          <t>не оплачено до 01.10.2026</t>
-        </is>
-      </c>
-      <c r="B65" s="36" t="n">
-        <v>46294</v>
-      </c>
-      <c r="C65" s="37" t="n"/>
-      <c r="D65" s="37" t="n"/>
-      <c r="E65" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="39" t="n">
-        <v>185.20833</v>
-      </c>
-      <c r="G65" s="37" t="n"/>
-      <c r="H65" s="37" t="n"/>
-      <c r="I65" s="37" t="n"/>
-      <c r="J65" s="37" t="n"/>
-      <c r="K65" s="37" t="n"/>
-      <c r="L65" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="39" t="n">
-        <v>185.20833</v>
-      </c>
-      <c r="N65" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O65" s="40" t="inlineStr">
-        <is>
-          <t>Просрочен</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="35" t="inlineStr">
-        <is>
-          <t>платёж 29.10.2026</t>
-        </is>
-      </c>
-      <c r="B66" s="36" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C66" s="37" t="n"/>
-      <c r="D66" s="37" t="n"/>
-      <c r="E66" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="37" t="n"/>
-      <c r="G66" s="39" t="n">
-        <v>191.77083</v>
-      </c>
-      <c r="H66" s="39" t="n">
-        <v>145.83333</v>
-      </c>
-      <c r="I66" s="39" t="n">
-        <v>45.9375</v>
-      </c>
-      <c r="J66" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="39" t="n">
-        <v>191.77083</v>
-      </c>
-      <c r="N66" s="37" t="n"/>
-      <c r="O66" s="40" t="inlineStr">
-        <is>
-          <t>Не наступил</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Ош-Текстиль»</t>
-        </is>
-      </c>
-      <c r="B67" s="29" t="n"/>
-      <c r="C67" s="30" t="n"/>
-      <c r="D67" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>1610</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>208.92857</v>
-      </c>
-      <c r="H67" s="32" t="n">
-        <v>171.42857</v>
-      </c>
-      <c r="I67" s="32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>1818.92857</v>
-      </c>
-      <c r="N67" s="31" t="n">
-        <v>212</v>
-      </c>
-      <c r="O67" s="33" t="n"/>
-    </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="34" t="inlineStr">
-        <is>
-          <t>№ 21-5/203 от 09.09.2021, KGS</t>
-        </is>
-      </c>
-      <c r="B68" s="29" t="n"/>
-      <c r="C68" s="30" t="n"/>
-      <c r="D68" s="30" t="n"/>
-      <c r="E68" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>1610</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>208.92857</v>
-      </c>
-      <c r="H68" s="32" t="n">
-        <v>171.42857</v>
-      </c>
-      <c r="I68" s="32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J68" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>1818.92857</v>
-      </c>
-      <c r="N68" s="31" t="n">
-        <v>212</v>
-      </c>
-      <c r="O68" s="33" t="n"/>
     </row>
     <row r="69" ht="13" customHeight="1">
       <c r="A69" s="35" t="inlineStr">
@@ -3370,15 +3366,15 @@
         </is>
       </c>
       <c r="B69" s="36" t="n">
-        <v>46084</v>
+        <v>46294</v>
       </c>
       <c r="C69" s="37" t="n"/>
       <c r="D69" s="37" t="n"/>
       <c r="E69" s="38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F69" s="39" t="n">
-        <v>1610</v>
+        <v>185.20833</v>
       </c>
       <c r="G69" s="37" t="n"/>
       <c r="H69" s="37" t="n"/>
@@ -3389,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="M69" s="39" t="n">
-        <v>1610</v>
+        <v>185.20833</v>
       </c>
       <c r="N69" s="38" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="O69" s="40" t="inlineStr">
         <is>
@@ -3403,11 +3399,11 @@
     <row r="70" ht="13" customHeight="1">
       <c r="A70" s="35" t="inlineStr">
         <is>
-          <t>платёж 03.10.2026</t>
+          <t>платёж 29.10.2026</t>
         </is>
       </c>
       <c r="B70" s="36" t="n">
-        <v>46298</v>
+        <v>46324</v>
       </c>
       <c r="C70" s="37" t="n"/>
       <c r="D70" s="37" t="n"/>
@@ -3416,13 +3412,13 @@
       </c>
       <c r="F70" s="37" t="n"/>
       <c r="G70" s="39" t="n">
-        <v>208.92857</v>
+        <v>191.77083</v>
       </c>
       <c r="H70" s="39" t="n">
-        <v>171.42857</v>
+        <v>145.83333</v>
       </c>
       <c r="I70" s="39" t="n">
-        <v>37.5</v>
+        <v>45.9375</v>
       </c>
       <c r="J70" s="39" t="n">
         <v>0</v>
@@ -3434,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="39" t="n">
-        <v>208.92857</v>
+        <v>191.77083</v>
       </c>
       <c r="N70" s="37" t="n"/>
       <c r="O70" s="40" t="inlineStr">
@@ -3444,73 +3440,71 @@
       </c>
     </row>
     <row r="71" ht="13" customHeight="1">
-      <c r="A71" s="22" t="inlineStr">
-        <is>
-          <t>Токтогулова Г. А.</t>
-        </is>
-      </c>
-      <c r="B71" s="23" t="n"/>
-      <c r="C71" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" s="24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F71" s="25" t="n">
-        <v>520</v>
-      </c>
-      <c r="G71" s="25" t="n">
-        <v>254.65328</v>
-      </c>
-      <c r="H71" s="25" t="n">
-        <v>207.14286</v>
-      </c>
-      <c r="I71" s="25" t="n">
-        <v>47.51042</v>
-      </c>
-      <c r="J71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="25" t="n">
-        <v>774.65328</v>
-      </c>
-      <c r="N71" s="26" t="n"/>
-      <c r="O71" s="27" t="n"/>
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Текстиль»</t>
+        </is>
+      </c>
+      <c r="B71" s="29" t="n"/>
+      <c r="C71" s="30" t="n"/>
+      <c r="D71" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>208.92857</v>
+      </c>
+      <c r="H71" s="32" t="n">
+        <v>171.42857</v>
+      </c>
+      <c r="I71" s="32" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>1818.92857</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>212</v>
+      </c>
+      <c r="O71" s="33" t="n"/>
     </row>
     <row r="72" ht="13" customHeight="1">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Ала-Тоо Агро»</t>
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>№ 21-5/203 от 09.09.2021, KGS</t>
         </is>
       </c>
       <c r="B72" s="29" t="n"/>
       <c r="C72" s="30" t="n"/>
-      <c r="D72" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="D72" s="30" t="n"/>
       <c r="E72" s="31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>115.84375</v>
+        <v>208.92857</v>
       </c>
       <c r="H72" s="32" t="n">
-        <v>100</v>
+        <v>171.42857</v>
       </c>
       <c r="I72" s="32" t="n">
-        <v>15.84375</v>
+        <v>37.5</v>
       </c>
       <c r="J72" s="32" t="n">
         <v>0</v>
@@ -3522,58 +3516,58 @@
         <v>0</v>
       </c>
       <c r="M72" s="32" t="n">
-        <v>115.84375</v>
-      </c>
-      <c r="N72" s="30" t="n"/>
+        <v>1818.92857</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>212</v>
+      </c>
       <c r="O72" s="33" t="n"/>
     </row>
     <row r="73" ht="13" customHeight="1">
-      <c r="A73" s="34" t="inlineStr">
-        <is>
-          <t>№ 25-4/030 от 10.02.2025, KGS</t>
-        </is>
-      </c>
-      <c r="B73" s="29" t="n"/>
-      <c r="C73" s="30" t="n"/>
-      <c r="D73" s="30" t="n"/>
-      <c r="E73" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>115.84375</v>
-      </c>
-      <c r="H73" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="I73" s="32" t="n">
-        <v>15.84375</v>
-      </c>
-      <c r="J73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>115.84375</v>
-      </c>
-      <c r="N73" s="30" t="n"/>
-      <c r="O73" s="33" t="n"/>
+      <c r="A73" s="35" t="inlineStr">
+        <is>
+          <t>не оплачено до 01.10.2026</t>
+        </is>
+      </c>
+      <c r="B73" s="36" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C73" s="37" t="n"/>
+      <c r="D73" s="37" t="n"/>
+      <c r="E73" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F73" s="39" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G73" s="37" t="n"/>
+      <c r="H73" s="37" t="n"/>
+      <c r="I73" s="37" t="n"/>
+      <c r="J73" s="37" t="n"/>
+      <c r="K73" s="37" t="n"/>
+      <c r="L73" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="39" t="n">
+        <v>1610</v>
+      </c>
+      <c r="N73" s="38" t="n">
+        <v>212</v>
+      </c>
+      <c r="O73" s="40" t="inlineStr">
+        <is>
+          <t>Просрочен</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="13" customHeight="1">
       <c r="A74" s="35" t="inlineStr">
         <is>
-          <t>платёж 10.10.2026</t>
+          <t>платёж 03.10.2026</t>
         </is>
       </c>
       <c r="B74" s="36" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="C74" s="37" t="n"/>
       <c r="D74" s="37" t="n"/>
@@ -3582,13 +3576,13 @@
       </c>
       <c r="F74" s="37" t="n"/>
       <c r="G74" s="39" t="n">
-        <v>115.84375</v>
+        <v>208.92857</v>
       </c>
       <c r="H74" s="39" t="n">
-        <v>100</v>
+        <v>171.42857</v>
       </c>
       <c r="I74" s="39" t="n">
-        <v>15.84375</v>
+        <v>37.5</v>
       </c>
       <c r="J74" s="39" t="n">
         <v>0</v>
@@ -3600,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="39" t="n">
-        <v>115.84375</v>
+        <v>208.92857</v>
       </c>
       <c r="N74" s="37" t="n"/>
       <c r="O74" s="40" t="inlineStr">
@@ -3610,55 +3604,59 @@
       </c>
     </row>
     <row r="75" ht="13" customHeight="1">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Каракол-Сервис»</t>
-        </is>
-      </c>
-      <c r="B75" s="29" t="n"/>
-      <c r="C75" s="30" t="n"/>
-      <c r="D75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="H75" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="I75" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="N75" s="30" t="n"/>
-      <c r="O75" s="33" t="n"/>
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>Токтогулова Г. А.</t>
+        </is>
+      </c>
+      <c r="B75" s="23" t="n"/>
+      <c r="C75" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="25" t="n">
+        <v>520</v>
+      </c>
+      <c r="G75" s="25" t="n">
+        <v>254.65328</v>
+      </c>
+      <c r="H75" s="25" t="n">
+        <v>207.14286</v>
+      </c>
+      <c r="I75" s="25" t="n">
+        <v>47.51042</v>
+      </c>
+      <c r="J75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="25" t="n">
+        <v>774.65328</v>
+      </c>
+      <c r="N75" s="26" t="n"/>
+      <c r="O75" s="27" t="n"/>
     </row>
     <row r="76" ht="13" customHeight="1">
-      <c r="A76" s="34" t="inlineStr">
-        <is>
-          <t>№ 25-3/014 от 05.03.2025, KGS</t>
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Тоо Агро»</t>
         </is>
       </c>
       <c r="B76" s="29" t="n"/>
       <c r="C76" s="30" t="n"/>
-      <c r="D76" s="30" t="n"/>
+      <c r="D76" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="E76" s="31" t="n">
         <v>1</v>
       </c>
@@ -3666,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G76" s="32" t="n">
-        <v>58.75</v>
+        <v>115.84375</v>
       </c>
       <c r="H76" s="32" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I76" s="32" t="n">
-        <v>8.75</v>
+        <v>15.84375</v>
       </c>
       <c r="J76" s="32" t="n">
         <v>0</v>
@@ -3684,120 +3682,118 @@
         <v>0</v>
       </c>
       <c r="M76" s="32" t="n">
-        <v>58.75</v>
+        <v>115.84375</v>
       </c>
       <c r="N76" s="30" t="n"/>
       <c r="O76" s="33" t="n"/>
     </row>
     <row r="77" ht="13" customHeight="1">
-      <c r="A77" s="35" t="inlineStr">
-        <is>
-          <t>платёж 05.10.2026</t>
-        </is>
-      </c>
-      <c r="B77" s="36" t="n">
-        <v>46300</v>
-      </c>
-      <c r="C77" s="37" t="n"/>
-      <c r="D77" s="37" t="n"/>
-      <c r="E77" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="37" t="n"/>
-      <c r="G77" s="39" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="H77" s="39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I77" s="39" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J77" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="39" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="N77" s="37" t="n"/>
-      <c r="O77" s="40" t="inlineStr">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>№ 25-4/030 от 10.02.2025, KGS</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="n"/>
+      <c r="C77" s="30" t="n"/>
+      <c r="D77" s="30" t="n"/>
+      <c r="E77" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>115.84375</v>
+      </c>
+      <c r="H77" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I77" s="32" t="n">
+        <v>15.84375</v>
+      </c>
+      <c r="J77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>115.84375</v>
+      </c>
+      <c r="N77" s="30" t="n"/>
+      <c r="O77" s="33" t="n"/>
+    </row>
+    <row r="78" ht="13" customHeight="1">
+      <c r="A78" s="35" t="inlineStr">
+        <is>
+          <t>платёж 10.10.2026</t>
+        </is>
+      </c>
+      <c r="B78" s="36" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C78" s="37" t="n"/>
+      <c r="D78" s="37" t="n"/>
+      <c r="E78" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="37" t="n"/>
+      <c r="G78" s="39" t="n">
+        <v>115.84375</v>
+      </c>
+      <c r="H78" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="I78" s="39" t="n">
+        <v>15.84375</v>
+      </c>
+      <c r="J78" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="39" t="n">
+        <v>115.84375</v>
+      </c>
+      <c r="N78" s="37" t="n"/>
+      <c r="O78" s="40" t="inlineStr">
         <is>
           <t>Не наступил</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="13" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Нарын-Сүт»</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="n"/>
-      <c r="C78" s="30" t="n"/>
-      <c r="D78" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>520</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>80.05953</v>
-      </c>
-      <c r="H78" s="32" t="n">
-        <v>57.14286</v>
-      </c>
-      <c r="I78" s="32" t="n">
-        <v>22.91667</v>
-      </c>
-      <c r="J78" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>600.05953</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>190</v>
-      </c>
-      <c r="O78" s="33" t="n"/>
-    </row>
     <row r="79" ht="13" customHeight="1">
-      <c r="A79" s="34" t="inlineStr">
-        <is>
-          <t>№ 23-5/071 от 09.08.2023, KGS</t>
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Каракол-Сервис»</t>
         </is>
       </c>
       <c r="B79" s="29" t="n"/>
       <c r="C79" s="30" t="n"/>
-      <c r="D79" s="30" t="n"/>
+      <c r="D79" s="31" t="n">
+        <v>1</v>
+      </c>
       <c r="E79" s="31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F79" s="32" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="G79" s="32" t="n">
-        <v>80.05953</v>
+        <v>58.75</v>
       </c>
       <c r="H79" s="32" t="n">
-        <v>57.14286</v>
+        <v>50</v>
       </c>
       <c r="I79" s="32" t="n">
-        <v>22.91667</v>
+        <v>8.75</v>
       </c>
       <c r="J79" s="32" t="n">
         <v>0</v>
@@ -3809,58 +3805,58 @@
         <v>0</v>
       </c>
       <c r="M79" s="32" t="n">
-        <v>600.05953</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>190</v>
-      </c>
+        <v>58.75</v>
+      </c>
+      <c r="N79" s="30" t="n"/>
       <c r="O79" s="33" t="n"/>
     </row>
     <row r="80" ht="13" customHeight="1">
-      <c r="A80" s="35" t="inlineStr">
-        <is>
-          <t>не оплачено до 01.10.2026</t>
-        </is>
-      </c>
-      <c r="B80" s="36" t="n">
-        <v>46106</v>
-      </c>
-      <c r="C80" s="37" t="n"/>
-      <c r="D80" s="37" t="n"/>
-      <c r="E80" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="F80" s="39" t="n">
-        <v>520</v>
-      </c>
-      <c r="G80" s="37" t="n"/>
-      <c r="H80" s="37" t="n"/>
-      <c r="I80" s="37" t="n"/>
-      <c r="J80" s="37" t="n"/>
-      <c r="K80" s="37" t="n"/>
-      <c r="L80" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="39" t="n">
-        <v>520</v>
-      </c>
-      <c r="N80" s="38" t="n">
-        <v>190</v>
-      </c>
-      <c r="O80" s="40" t="inlineStr">
-        <is>
-          <t>Просрочен</t>
-        </is>
-      </c>
+      <c r="A80" s="34" t="inlineStr">
+        <is>
+          <t>№ 25-3/014 от 05.03.2025, KGS</t>
+        </is>
+      </c>
+      <c r="B80" s="29" t="n"/>
+      <c r="C80" s="30" t="n"/>
+      <c r="D80" s="30" t="n"/>
+      <c r="E80" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="H80" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I80" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="N80" s="30" t="n"/>
+      <c r="O80" s="33" t="n"/>
     </row>
     <row r="81" ht="13" customHeight="1">
       <c r="A81" s="35" t="inlineStr">
         <is>
-          <t>платёж 25.10.2026</t>
+          <t>платёж 05.10.2026</t>
         </is>
       </c>
       <c r="B81" s="36" t="n">
-        <v>46320</v>
+        <v>46300</v>
       </c>
       <c r="C81" s="37" t="n"/>
       <c r="D81" s="37" t="n"/>
@@ -3869,13 +3865,13 @@
       </c>
       <c r="F81" s="37" t="n"/>
       <c r="G81" s="39" t="n">
-        <v>80.05953</v>
+        <v>58.75</v>
       </c>
       <c r="H81" s="39" t="n">
-        <v>57.14286</v>
+        <v>50</v>
       </c>
       <c r="I81" s="39" t="n">
-        <v>22.91667</v>
+        <v>8.75</v>
       </c>
       <c r="J81" s="39" t="n">
         <v>0</v>
@@ -3887,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="39" t="n">
-        <v>80.05953</v>
+        <v>58.75</v>
       </c>
       <c r="N81" s="37" t="n"/>
       <c r="O81" s="40" t="inlineStr">
@@ -3897,259 +3893,259 @@
       </c>
     </row>
     <row r="82" ht="13" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Нарын-Сүт»</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="n"/>
+      <c r="C82" s="30" t="n"/>
+      <c r="D82" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>520</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>80.05953</v>
+      </c>
+      <c r="H82" s="32" t="n">
+        <v>57.14286</v>
+      </c>
+      <c r="I82" s="32" t="n">
+        <v>22.91667</v>
+      </c>
+      <c r="J82" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>600.05953</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>190</v>
+      </c>
+      <c r="O82" s="33" t="n"/>
+    </row>
+    <row r="83" ht="13" customHeight="1">
+      <c r="A83" s="34" t="inlineStr">
+        <is>
+          <t>№ 23-5/071 от 09.08.2023, KGS</t>
+        </is>
+      </c>
+      <c r="B83" s="29" t="n"/>
+      <c r="C83" s="30" t="n"/>
+      <c r="D83" s="30" t="n"/>
+      <c r="E83" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F83" s="32" t="n">
+        <v>520</v>
+      </c>
+      <c r="G83" s="32" t="n">
+        <v>80.05953</v>
+      </c>
+      <c r="H83" s="32" t="n">
+        <v>57.14286</v>
+      </c>
+      <c r="I83" s="32" t="n">
+        <v>22.91667</v>
+      </c>
+      <c r="J83" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="32" t="n">
+        <v>600.05953</v>
+      </c>
+      <c r="N83" s="31" t="n">
+        <v>190</v>
+      </c>
+      <c r="O83" s="33" t="n"/>
+    </row>
+    <row r="84" ht="13" customHeight="1">
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t>не оплачено до 01.10.2026</t>
+        </is>
+      </c>
+      <c r="B84" s="36" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C84" s="37" t="n"/>
+      <c r="D84" s="37" t="n"/>
+      <c r="E84" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F84" s="39" t="n">
+        <v>520</v>
+      </c>
+      <c r="G84" s="37" t="n"/>
+      <c r="H84" s="37" t="n"/>
+      <c r="I84" s="37" t="n"/>
+      <c r="J84" s="37" t="n"/>
+      <c r="K84" s="37" t="n"/>
+      <c r="L84" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="39" t="n">
+        <v>520</v>
+      </c>
+      <c r="N84" s="38" t="n">
+        <v>190</v>
+      </c>
+      <c r="O84" s="40" t="inlineStr">
+        <is>
+          <t>Просрочен</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="13" customHeight="1">
+      <c r="A85" s="35" t="inlineStr">
+        <is>
+          <t>платёж 25.10.2026</t>
+        </is>
+      </c>
+      <c r="B85" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C85" s="37" t="n"/>
+      <c r="D85" s="37" t="n"/>
+      <c r="E85" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="37" t="n"/>
+      <c r="G85" s="39" t="n">
+        <v>80.05953</v>
+      </c>
+      <c r="H85" s="39" t="n">
+        <v>57.14286</v>
+      </c>
+      <c r="I85" s="39" t="n">
+        <v>22.91667</v>
+      </c>
+      <c r="J85" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="39" t="n">
+        <v>80.05953</v>
+      </c>
+      <c r="N85" s="37" t="n"/>
+      <c r="O85" s="40" t="inlineStr">
+        <is>
+          <t>Не наступил</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="13" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Отдел развития АПК</t>
         </is>
       </c>
-      <c r="B82" s="17" t="n"/>
-      <c r="C82" s="18" t="n">
+      <c r="B86" s="17" t="n"/>
+      <c r="C86" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D82" s="18" t="n">
+      <c r="D86" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E82" s="18" t="n">
+      <c r="E86" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="F82" s="19" t="n">
+      <c r="F86" s="19" t="n">
         <v>1825.5</v>
       </c>
-      <c r="G82" s="19" t="n">
+      <c r="G86" s="19" t="n">
         <v>247.66667</v>
       </c>
-      <c r="H82" s="19" t="n">
+      <c r="H86" s="19" t="n">
         <v>176.66667</v>
       </c>
-      <c r="I82" s="19" t="n">
+      <c r="I86" s="19" t="n">
         <v>71</v>
       </c>
-      <c r="J82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="19" t="n">
+      <c r="J86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="19" t="n">
         <v>2073.16667</v>
       </c>
-      <c r="N82" s="20" t="n"/>
-      <c r="O82" s="21" t="n"/>
-    </row>
-    <row r="83" ht="13" customHeight="1">
-      <c r="A83" s="22" t="inlineStr">
+      <c r="N86" s="20" t="n"/>
+      <c r="O86" s="21" t="n"/>
+    </row>
+    <row r="87" ht="13" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
         <is>
           <t>Жумабаев Р. С.</t>
         </is>
       </c>
-      <c r="B83" s="23" t="n"/>
-      <c r="C83" s="24" t="n">
+      <c r="B87" s="23" t="n"/>
+      <c r="C87" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="D83" s="24" t="n">
+      <c r="D87" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="E83" s="24" t="n">
+      <c r="E87" s="24" t="n">
         <v>31</v>
       </c>
-      <c r="F83" s="25" t="n">
+      <c r="F87" s="25" t="n">
         <v>1825.5</v>
       </c>
-      <c r="G83" s="25" t="n">
+      <c r="G87" s="25" t="n">
         <v>247.66667</v>
       </c>
-      <c r="H83" s="25" t="n">
+      <c r="H87" s="25" t="n">
         <v>176.66667</v>
       </c>
-      <c r="I83" s="25" t="n">
+      <c r="I87" s="25" t="n">
         <v>71</v>
       </c>
-      <c r="J83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="25" t="n">
+      <c r="J87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="25" t="n">
         <v>2073.16667</v>
       </c>
-      <c r="N83" s="26" t="n"/>
-      <c r="O83" s="27" t="n"/>
-    </row>
-    <row r="84" ht="13" customHeight="1">
-      <c r="A84" s="28" t="inlineStr">
-        <is>
-          <t>Иманалиев Бакыт Тологонович</t>
-        </is>
-      </c>
-      <c r="B84" s="29" t="n"/>
-      <c r="C84" s="30" t="n"/>
-      <c r="D84" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" s="32" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G84" s="32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H84" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="I84" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J84" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="32" t="n">
-        <v>64</v>
-      </c>
-      <c r="N84" s="31" t="n">
-        <v>95</v>
-      </c>
-      <c r="O84" s="33" t="n"/>
-    </row>
-    <row r="85" ht="13" customHeight="1">
-      <c r="A85" s="34" t="inlineStr">
-        <is>
-          <t>№ 24-2/077 от 14.05.2024, KGS</t>
-        </is>
-      </c>
-      <c r="B85" s="29" t="n"/>
-      <c r="C85" s="30" t="n"/>
-      <c r="D85" s="30" t="n"/>
-      <c r="E85" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F85" s="32" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G85" s="32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H85" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="I85" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J85" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="32" t="n">
-        <v>64</v>
-      </c>
-      <c r="N85" s="31" t="n">
-        <v>95</v>
-      </c>
-      <c r="O85" s="33" t="n"/>
-    </row>
-    <row r="86" ht="13" customHeight="1">
-      <c r="A86" s="35" t="inlineStr">
-        <is>
-          <t>не оплачено до 01.10.2026</t>
-        </is>
-      </c>
-      <c r="B86" s="36" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C86" s="37" t="n"/>
-      <c r="D86" s="37" t="n"/>
-      <c r="E86" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="F86" s="39" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G86" s="37" t="n"/>
-      <c r="H86" s="37" t="n"/>
-      <c r="I86" s="37" t="n"/>
-      <c r="J86" s="37" t="n"/>
-      <c r="K86" s="37" t="n"/>
-      <c r="L86" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="39" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N86" s="38" t="n">
-        <v>95</v>
-      </c>
-      <c r="O86" s="40" t="inlineStr">
-        <is>
-          <t>Просрочен</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="13" customHeight="1">
-      <c r="A87" s="35" t="inlineStr">
-        <is>
-          <t>платёж 28.10.2026</t>
-        </is>
-      </c>
-      <c r="B87" s="36" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C87" s="37" t="n"/>
-      <c r="D87" s="37" t="n"/>
-      <c r="E87" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="37" t="n"/>
-      <c r="G87" s="39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H87" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="I87" s="39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J87" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="N87" s="37" t="n"/>
-      <c r="O87" s="40" t="inlineStr">
-        <is>
-          <t>Не наступил</t>
-        </is>
-      </c>
+      <c r="N87" s="26" t="n"/>
+      <c r="O87" s="27" t="n"/>
     </row>
     <row r="88" ht="13" customHeight="1">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>ОсОО «Нарын-Агро»</t>
+          <t>Иманалиев Бакыт Тологонович</t>
         </is>
       </c>
       <c r="B88" s="29" t="n"/>
@@ -4158,19 +4154,19 @@
         <v>1</v>
       </c>
       <c r="E88" s="31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F88" s="32" t="n">
-        <v>960</v>
+        <v>50.5</v>
       </c>
       <c r="G88" s="32" t="n">
-        <v>71.875</v>
+        <v>13.5</v>
       </c>
       <c r="H88" s="32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I88" s="32" t="n">
-        <v>21.875</v>
+        <v>3.5</v>
       </c>
       <c r="J88" s="32" t="n">
         <v>0</v>
@@ -4182,36 +4178,36 @@
         <v>0</v>
       </c>
       <c r="M88" s="32" t="n">
-        <v>1031.875</v>
+        <v>64</v>
       </c>
       <c r="N88" s="31" t="n">
-        <v>409</v>
+        <v>95</v>
       </c>
       <c r="O88" s="33" t="n"/>
     </row>
     <row r="89" ht="13" customHeight="1">
       <c r="A89" s="34" t="inlineStr">
         <is>
-          <t>№ 21-2/077 от 18.05.2021, KGS</t>
+          <t>№ 24-2/077 от 14.05.2024, KGS</t>
         </is>
       </c>
       <c r="B89" s="29" t="n"/>
       <c r="C89" s="30" t="n"/>
       <c r="D89" s="30" t="n"/>
       <c r="E89" s="31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F89" s="32" t="n">
-        <v>960</v>
+        <v>50.5</v>
       </c>
       <c r="G89" s="32" t="n">
-        <v>71.875</v>
+        <v>13.5</v>
       </c>
       <c r="H89" s="32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I89" s="32" t="n">
-        <v>21.875</v>
+        <v>3.5</v>
       </c>
       <c r="J89" s="32" t="n">
         <v>0</v>
@@ -4223,29 +4219,29 @@
         <v>0</v>
       </c>
       <c r="M89" s="32" t="n">
-        <v>1031.875</v>
+        <v>64</v>
       </c>
       <c r="N89" s="31" t="n">
-        <v>409</v>
+        <v>95</v>
       </c>
       <c r="O89" s="33" t="n"/>
     </row>
     <row r="90" ht="13" customHeight="1">
       <c r="A90" s="35" t="inlineStr">
         <is>
-          <t>не оплачено до 01.10.2026, в суде</t>
+          <t>не оплачено до 01.10.2026</t>
         </is>
       </c>
       <c r="B90" s="36" t="n">
-        <v>45887</v>
+        <v>46201</v>
       </c>
       <c r="C90" s="37" t="n"/>
       <c r="D90" s="37" t="n"/>
       <c r="E90" s="38" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F90" s="39" t="n">
-        <v>960</v>
+        <v>50.5</v>
       </c>
       <c r="G90" s="37" t="n"/>
       <c r="H90" s="37" t="n"/>
@@ -4256,25 +4252,25 @@
         <v>0</v>
       </c>
       <c r="M90" s="39" t="n">
-        <v>960</v>
+        <v>50.5</v>
       </c>
       <c r="N90" s="38" t="n">
-        <v>409</v>
+        <v>95</v>
       </c>
       <c r="O90" s="40" t="inlineStr">
         <is>
-          <t>Предъявлен в суд</t>
+          <t>Просрочен</t>
         </is>
       </c>
     </row>
     <row r="91" ht="13" customHeight="1">
       <c r="A91" s="35" t="inlineStr">
         <is>
-          <t>платёж 18.10.2026</t>
+          <t>платёж 28.10.2026</t>
         </is>
       </c>
       <c r="B91" s="36" t="n">
-        <v>46313</v>
+        <v>46323</v>
       </c>
       <c r="C91" s="37" t="n"/>
       <c r="D91" s="37" t="n"/>
@@ -4283,13 +4279,13 @@
       </c>
       <c r="F91" s="37" t="n"/>
       <c r="G91" s="39" t="n">
-        <v>71.875</v>
+        <v>13.5</v>
       </c>
       <c r="H91" s="39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I91" s="39" t="n">
-        <v>21.875</v>
+        <v>3.5</v>
       </c>
       <c r="J91" s="39" t="n">
         <v>0</v>
@@ -4301,73 +4297,81 @@
         <v>0</v>
       </c>
       <c r="M91" s="39" t="n">
-        <v>71.875</v>
+        <v>13.5</v>
       </c>
       <c r="N91" s="37" t="n"/>
       <c r="O91" s="40" t="inlineStr">
         <is>
-          <t>Предъявлен в суд</t>
+          <t>Не наступил</t>
         </is>
       </c>
     </row>
     <row r="92" ht="13" customHeight="1">
-      <c r="A92" s="41" t="inlineStr">
-        <is>
-          <t>по соглашению № 3: платёж 1 из 6</t>
-        </is>
-      </c>
-      <c r="B92" s="46" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C92" s="43" t="n"/>
-      <c r="D92" s="43" t="n"/>
-      <c r="E92" s="43" t="n"/>
-      <c r="F92" s="43" t="n"/>
-      <c r="G92" s="44" t="n">
-        <v>404.05</v>
-      </c>
-      <c r="H92" s="43" t="n"/>
-      <c r="I92" s="43" t="n"/>
-      <c r="J92" s="43" t="n"/>
-      <c r="K92" s="43" t="n"/>
-      <c r="L92" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="44" t="n">
-        <v>404.05</v>
-      </c>
-      <c r="N92" s="43" t="n"/>
-      <c r="O92" s="45" t="inlineStr">
-        <is>
-          <t>Не наступил</t>
-        </is>
-      </c>
+      <c r="A92" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Нарын-Агро»</t>
+        </is>
+      </c>
+      <c r="B92" s="29" t="n"/>
+      <c r="C92" s="30" t="n"/>
+      <c r="D92" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F92" s="32" t="n">
+        <v>960</v>
+      </c>
+      <c r="G92" s="32" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="H92" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I92" s="32" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="J92" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="32" t="n">
+        <v>1031.875</v>
+      </c>
+      <c r="N92" s="31" t="n">
+        <v>409</v>
+      </c>
+      <c r="O92" s="33" t="n"/>
     </row>
     <row r="93" ht="13" customHeight="1">
-      <c r="A93" s="28" t="inlineStr">
-        <is>
-          <t>ОсОО «Талас-Бал»</t>
+      <c r="A93" s="34" t="inlineStr">
+        <is>
+          <t>№ 21-2/077 от 18.05.2021, KGS</t>
         </is>
       </c>
       <c r="B93" s="29" t="n"/>
       <c r="C93" s="30" t="n"/>
-      <c r="D93" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="D93" s="30" t="n"/>
       <c r="E93" s="31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F93" s="32" t="n">
-        <v>815</v>
+        <v>960</v>
       </c>
       <c r="G93" s="32" t="n">
-        <v>90.625</v>
+        <v>71.875</v>
       </c>
       <c r="H93" s="32" t="n">
-        <v>66.66667</v>
+        <v>50</v>
       </c>
       <c r="I93" s="32" t="n">
-        <v>23.95833</v>
+        <v>21.875</v>
       </c>
       <c r="J93" s="32" t="n">
         <v>0</v>
@@ -4379,129 +4383,121 @@
         <v>0</v>
       </c>
       <c r="M93" s="32" t="n">
-        <v>905.625</v>
+        <v>1031.875</v>
       </c>
       <c r="N93" s="31" t="n">
-        <v>260</v>
+        <v>409</v>
       </c>
       <c r="O93" s="33" t="n"/>
     </row>
     <row r="94" ht="13" customHeight="1">
-      <c r="A94" s="34" t="inlineStr">
-        <is>
-          <t>№ 23-4/021 от 21.08.2023, KGS</t>
-        </is>
-      </c>
-      <c r="B94" s="29" t="n"/>
-      <c r="C94" s="30" t="n"/>
-      <c r="D94" s="30" t="n"/>
-      <c r="E94" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F94" s="32" t="n">
-        <v>815</v>
-      </c>
-      <c r="G94" s="32" t="n">
-        <v>90.625</v>
-      </c>
-      <c r="H94" s="32" t="n">
-        <v>66.66667</v>
-      </c>
-      <c r="I94" s="32" t="n">
-        <v>23.95833</v>
-      </c>
-      <c r="J94" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="32" t="n">
-        <v>905.625</v>
-      </c>
-      <c r="N94" s="31" t="n">
-        <v>260</v>
-      </c>
-      <c r="O94" s="33" t="n"/>
+      <c r="A94" s="35" t="inlineStr">
+        <is>
+          <t>не оплачено до 01.10.2026, в суде</t>
+        </is>
+      </c>
+      <c r="B94" s="36" t="n">
+        <v>45887</v>
+      </c>
+      <c r="C94" s="37" t="n"/>
+      <c r="D94" s="37" t="n"/>
+      <c r="E94" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="F94" s="39" t="n">
+        <v>960</v>
+      </c>
+      <c r="G94" s="37" t="n"/>
+      <c r="H94" s="37" t="n"/>
+      <c r="I94" s="37" t="n"/>
+      <c r="J94" s="37" t="n"/>
+      <c r="K94" s="37" t="n"/>
+      <c r="L94" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="39" t="n">
+        <v>960</v>
+      </c>
+      <c r="N94" s="38" t="n">
+        <v>409</v>
+      </c>
+      <c r="O94" s="40" t="inlineStr">
+        <is>
+          <t>Предъявлен в суд</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="13" customHeight="1">
       <c r="A95" s="35" t="inlineStr">
         <is>
-          <t>не оплачено до 01.10.2026</t>
+          <t>платёж 18.10.2026</t>
         </is>
       </c>
       <c r="B95" s="36" t="n">
-        <v>46036</v>
+        <v>46313</v>
       </c>
       <c r="C95" s="37" t="n"/>
       <c r="D95" s="37" t="n"/>
       <c r="E95" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="F95" s="39" t="n">
-        <v>815</v>
-      </c>
-      <c r="G95" s="37" t="n"/>
-      <c r="H95" s="37" t="n"/>
-      <c r="I95" s="37" t="n"/>
-      <c r="J95" s="37" t="n"/>
-      <c r="K95" s="37" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F95" s="37" t="n"/>
+      <c r="G95" s="39" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="H95" s="39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I95" s="39" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="J95" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" s="39" t="n">
         <v>0</v>
       </c>
       <c r="M95" s="39" t="n">
-        <v>815</v>
-      </c>
-      <c r="N95" s="38" t="n">
-        <v>260</v>
-      </c>
+        <v>71.875</v>
+      </c>
+      <c r="N95" s="37" t="n"/>
       <c r="O95" s="40" t="inlineStr">
         <is>
-          <t>Просрочен</t>
+          <t>Предъявлен в суд</t>
         </is>
       </c>
     </row>
     <row r="96" ht="13" customHeight="1">
-      <c r="A96" s="35" t="inlineStr">
-        <is>
-          <t>платёж 14.10.2026</t>
-        </is>
-      </c>
-      <c r="B96" s="36" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C96" s="37" t="n"/>
-      <c r="D96" s="37" t="n"/>
-      <c r="E96" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="37" t="n"/>
-      <c r="G96" s="39" t="n">
-        <v>90.625</v>
-      </c>
-      <c r="H96" s="39" t="n">
-        <v>66.66667</v>
-      </c>
-      <c r="I96" s="39" t="n">
-        <v>23.95833</v>
-      </c>
-      <c r="J96" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="39" t="n">
-        <v>90.625</v>
-      </c>
-      <c r="N96" s="37" t="n"/>
-      <c r="O96" s="40" t="inlineStr">
+      <c r="A96" s="41" t="inlineStr">
+        <is>
+          <t>по соглашению № 3: платёж 1 из 6</t>
+        </is>
+      </c>
+      <c r="B96" s="46" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C96" s="43" t="n"/>
+      <c r="D96" s="43" t="n"/>
+      <c r="E96" s="43" t="n"/>
+      <c r="F96" s="43" t="n"/>
+      <c r="G96" s="44" t="n">
+        <v>404.05</v>
+      </c>
+      <c r="H96" s="43" t="n"/>
+      <c r="I96" s="43" t="n"/>
+      <c r="J96" s="43" t="n"/>
+      <c r="K96" s="43" t="n"/>
+      <c r="L96" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="44" t="n">
+        <v>404.05</v>
+      </c>
+      <c r="N96" s="43" t="n"/>
+      <c r="O96" s="45" t="inlineStr">
         <is>
           <t>Не наступил</t>
         </is>
@@ -4510,7 +4506,7 @@
     <row r="97" ht="13" customHeight="1">
       <c r="A97" s="28" t="inlineStr">
         <is>
-          <t>ОсОО «Ысык-Көл Логистик»</t>
+          <t>ОсОО «Талас-Бал»</t>
         </is>
       </c>
       <c r="B97" s="29" t="n"/>
@@ -4519,19 +4515,19 @@
         <v>1</v>
       </c>
       <c r="E97" s="31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F97" s="32" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="G97" s="32" t="n">
-        <v>71.66667</v>
+        <v>90.625</v>
       </c>
       <c r="H97" s="32" t="n">
-        <v>50</v>
+        <v>66.66667</v>
       </c>
       <c r="I97" s="32" t="n">
-        <v>21.66667</v>
+        <v>23.95833</v>
       </c>
       <c r="J97" s="32" t="n">
         <v>0</v>
@@ -4543,34 +4539,36 @@
         <v>0</v>
       </c>
       <c r="M97" s="32" t="n">
-        <v>71.66667</v>
-      </c>
-      <c r="N97" s="30" t="n"/>
+        <v>905.625</v>
+      </c>
+      <c r="N97" s="31" t="n">
+        <v>260</v>
+      </c>
       <c r="O97" s="33" t="n"/>
     </row>
     <row r="98" ht="13" customHeight="1">
       <c r="A98" s="34" t="inlineStr">
         <is>
-          <t>№ 21-6/144 от 02.06.2021, KGS</t>
+          <t>№ 23-4/021 от 21.08.2023, KGS</t>
         </is>
       </c>
       <c r="B98" s="29" t="n"/>
       <c r="C98" s="30" t="n"/>
       <c r="D98" s="30" t="n"/>
       <c r="E98" s="31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F98" s="32" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="G98" s="32" t="n">
-        <v>71.66667</v>
+        <v>90.625</v>
       </c>
       <c r="H98" s="32" t="n">
-        <v>50</v>
+        <v>66.66667</v>
       </c>
       <c r="I98" s="32" t="n">
-        <v>21.66667</v>
+        <v>23.95833</v>
       </c>
       <c r="J98" s="32" t="n">
         <v>0</v>
@@ -4582,49 +4580,211 @@
         <v>0</v>
       </c>
       <c r="M98" s="32" t="n">
-        <v>71.66667</v>
-      </c>
-      <c r="N98" s="30" t="n"/>
+        <v>905.625</v>
+      </c>
+      <c r="N98" s="31" t="n">
+        <v>260</v>
+      </c>
       <c r="O98" s="33" t="n"/>
     </row>
     <row r="99" ht="13" customHeight="1">
       <c r="A99" s="35" t="inlineStr">
         <is>
-          <t>платёж 02.10.2026</t>
+          <t>не оплачено до 01.10.2026</t>
         </is>
       </c>
       <c r="B99" s="36" t="n">
-        <v>46297</v>
+        <v>46036</v>
       </c>
       <c r="C99" s="37" t="n"/>
       <c r="D99" s="37" t="n"/>
       <c r="E99" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="37" t="n"/>
-      <c r="G99" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F99" s="39" t="n">
+        <v>815</v>
+      </c>
+      <c r="G99" s="37" t="n"/>
+      <c r="H99" s="37" t="n"/>
+      <c r="I99" s="37" t="n"/>
+      <c r="J99" s="37" t="n"/>
+      <c r="K99" s="37" t="n"/>
+      <c r="L99" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="39" t="n">
+        <v>815</v>
+      </c>
+      <c r="N99" s="38" t="n">
+        <v>260</v>
+      </c>
+      <c r="O99" s="40" t="inlineStr">
+        <is>
+          <t>Просрочен</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="13" customHeight="1">
+      <c r="A100" s="35" t="inlineStr">
+        <is>
+          <t>платёж 14.10.2026</t>
+        </is>
+      </c>
+      <c r="B100" s="36" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C100" s="37" t="n"/>
+      <c r="D100" s="37" t="n"/>
+      <c r="E100" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="37" t="n"/>
+      <c r="G100" s="39" t="n">
+        <v>90.625</v>
+      </c>
+      <c r="H100" s="39" t="n">
+        <v>66.66667</v>
+      </c>
+      <c r="I100" s="39" t="n">
+        <v>23.95833</v>
+      </c>
+      <c r="J100" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="39" t="n">
+        <v>90.625</v>
+      </c>
+      <c r="N100" s="37" t="n"/>
+      <c r="O100" s="40" t="inlineStr">
+        <is>
+          <t>Не наступил</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="13" customHeight="1">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>ОсОО «Ысык-Көл Логистик»</t>
+        </is>
+      </c>
+      <c r="B101" s="29" t="n"/>
+      <c r="C101" s="30" t="n"/>
+      <c r="D101" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="32" t="n">
         <v>71.66667</v>
       </c>
-      <c r="H99" s="39" t="n">
+      <c r="H101" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="I99" s="39" t="n">
+      <c r="I101" s="32" t="n">
         <v>21.66667</v>
       </c>
-      <c r="J99" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="39" t="n">
+      <c r="J101" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="32" t="n">
         <v>71.66667</v>
       </c>
-      <c r="N99" s="37" t="n"/>
-      <c r="O99" s="40" t="inlineStr">
+      <c r="N101" s="30" t="n"/>
+      <c r="O101" s="33" t="n"/>
+    </row>
+    <row r="102" ht="13" customHeight="1">
+      <c r="A102" s="34" t="inlineStr">
+        <is>
+          <t>№ 21-6/144 от 02.06.2021, KGS</t>
+        </is>
+      </c>
+      <c r="B102" s="29" t="n"/>
+      <c r="C102" s="30" t="n"/>
+      <c r="D102" s="30" t="n"/>
+      <c r="E102" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="32" t="n">
+        <v>71.66667</v>
+      </c>
+      <c r="H102" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I102" s="32" t="n">
+        <v>21.66667</v>
+      </c>
+      <c r="J102" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="32" t="n">
+        <v>71.66667</v>
+      </c>
+      <c r="N102" s="30" t="n"/>
+      <c r="O102" s="33" t="n"/>
+    </row>
+    <row r="103" ht="13" customHeight="1">
+      <c r="A103" s="35" t="inlineStr">
+        <is>
+          <t>платёж 02.10.2026</t>
+        </is>
+      </c>
+      <c r="B103" s="36" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C103" s="37" t="n"/>
+      <c r="D103" s="37" t="n"/>
+      <c r="E103" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="37" t="n"/>
+      <c r="G103" s="39" t="n">
+        <v>71.66667</v>
+      </c>
+      <c r="H103" s="39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I103" s="39" t="n">
+        <v>21.66667</v>
+      </c>
+      <c r="J103" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="39" t="n">
+        <v>71.66667</v>
+      </c>
+      <c r="N103" s="37" t="n"/>
+      <c r="O103" s="40" t="inlineStr">
         <is>
           <t>Не наступил</t>
         </is>
@@ -4824,7 +4984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5285,7 +5445,7 @@
       </c>
       <c r="B39" s="52" t="inlineStr">
         <is>
-          <t>Октябрь 2026, оплата на 01.10.2026: заёмщиков 19, кредитов 22, платежей по графику 92; «Не оплачено на начало периода» 9 805,365 тыс. сом, «По графику за период» 2 812,982, оплачено 0,000, осталось оплатить 12 618,347.</t>
+          <t>Октябрь 2026, оплата на 01.10.2026: заёмщиков 20, кредитов 23, платежей по графику 93; «Не оплачено на начало периода» 9 805,365 тыс. сом, «По графику за период» 2 850,009, оплачено 0,000, осталось оплатить 12 655,374.</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5485,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43" ht="75" customHeight="1">
       <c r="A43" s="51" t="inlineStr">
         <is>
           <t>5.</t>
@@ -5333,7 +5493,7 @@
       </c>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>За прошлый месяц ИТОГО «По графику за период» = «По графику за период» ФО-54 за тот же месяц. Сентябрь 2026: «Оплачено» = ИТОГО ФО-04 1 667,910 − досрочное погашение КЗ-15 сверх графика 250,000 + разница курса КЗ-11 0,528 (5,275 тыс. USD по 87,50 = 461,563 против 461,035 по курсу дня платежа) = 1 418,438 тыс. сом.</t>
+          <t>За прошлый месяц ИТОГО «По графику за период» = «По графику за период» ФО-54 за тот же месяц. Сентябрь 2026: «Оплачено» = ИТОГО ФО-04 1 706,077 (с платежом КЗ-25 21.09.2026 38,167) − досрочное погашение КЗ-15 сверх графика 250,000 + разница курса КЗ-11 0,528 (5,275 тыс. USD по 87,50 = 461,563 против 461,035 по курсу дня платежа) + разница курса КЗ-25 0,094 (376,96 EUR по 101,50 = 38,261 против 38,167 по 101,25) = 1 456,699 тыс. сом.</t>
         </is>
       </c>
     </row>
@@ -5393,11 +5553,11 @@
       </c>
       <c r="B48" s="52" t="inlineStr">
         <is>
-          <t>Валютные КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22 (EUR 101,50000): все суммы по курсу на 30.09.2026; под кредитом строка «в тыс. USD (курс 87,50000)» / «в тыс. EUR (курс 101,50000)».</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
+          <t>Валютные КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22, КЗ-25 (EUR 101,50000): все суммы по курсу на 30.09.2026; под кредитом строка «в тыс. USD (курс 87,50000)» / «в тыс. EUR (курс 101,50000)».</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="51" t="inlineStr">
         <is>
           <t>11.</t>
@@ -5405,24 +5565,36 @@
       </c>
       <c r="B49" s="52" t="inlineStr">
         <is>
+          <t>КЗ-25 № 21-9/040 (EUR, плавающая ставка): в октябре один платёж 20.10.2026 — только проценты за 21.09–20.10.2026, 30 дней по ставке на дату состояния 6,08 % (Euribor-6m 2,08 + 4,00), факт/360: 364,80 EUR = 37,027 тыс. сом; основной суммы в октябре по графику нет (20 марта ежегодно); платёж 20.09.2026 (срок 21.09.2026) оплачен 21.09.2026 — в отчёте за октябрь его нет; под Бековой Н. С. «Ала-Арча Энерго» перед «Кут-Мүлк».</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B50" s="52" t="inlineStr">
+        <is>
           <t>КЗ-07 — под заёмщиком на дату состояния ОсОО «Ысык-Көл Логистик» (долг переведён 09.09.2026); КЗ-17 — первый платёж 15.10.2026.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="51" t="inlineStr">
-        <is>
-          <t>12.</t>
-        </is>
-      </c>
-      <c r="B50" s="52" t="inlineStr">
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="51" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B51" s="52" t="inlineStr">
         <is>
           <t>Не показаны: КЗ-08 (списан 17.09.2026), КЗ-18 (расторгнут до выдачи), КЗ-15 (погашен 18.09.2026, в октябре платежей нет; в отчёте за сентябрь — платёж 18.09.2026 «Оплачен»), КЗ-16 и КЗ-24 (платежей по графику нет; у КЗ-24 остались только штрафы).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
@@ -5447,6 +5619,7 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="B41:C41"/>
